--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.78295751080257</v>
+        <v>5.327230595505418</v>
       </c>
       <c r="D2" t="n">
-        <v>32.95402283842533</v>
+        <v>5.355028711244117</v>
       </c>
       <c r="E2" t="n">
-        <v>26.50349386896836</v>
+        <v>4.306817753707358</v>
       </c>
       <c r="F2" t="n">
-        <v>11.7153754702581</v>
+        <v>1.903748513916942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.78796547629699</v>
+        <v>3.05304438989826</v>
       </c>
       <c r="D3" t="n">
-        <v>18.9999120697018</v>
+        <v>3.087485711326543</v>
       </c>
       <c r="E3" t="n">
-        <v>26.50349386896836</v>
+        <v>4.306817753707358</v>
       </c>
       <c r="F3" t="n">
-        <v>11.7153754702581</v>
+        <v>1.903748513916942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45362404707371</v>
+        <v>2.186213907649478</v>
       </c>
       <c r="D4" t="n">
-        <v>13.67464265389867</v>
+        <v>2.222129431258534</v>
       </c>
       <c r="E4" t="n">
-        <v>26.50349386896836</v>
+        <v>4.306817753707358</v>
       </c>
       <c r="F4" t="n">
-        <v>11.7153754702581</v>
+        <v>1.903748513916942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>79.21497234573343</v>
+        <v>12.87243300618168</v>
       </c>
       <c r="D5" t="n">
-        <v>44.23655934685181</v>
+        <v>7.188440893863419</v>
       </c>
       <c r="E5" t="n">
-        <v>26.50349386896836</v>
+        <v>4.306817753707358</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7153754702581</v>
+        <v>1.903748513916942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.26457438668734</v>
+        <v>11.09299333783669</v>
       </c>
       <c r="D6" t="n">
-        <v>39.3513523063264</v>
+        <v>6.394594749778041</v>
       </c>
       <c r="E6" t="n">
-        <v>26.50349386896836</v>
+        <v>4.306817753707358</v>
       </c>
       <c r="F6" t="n">
-        <v>11.7153754702581</v>
+        <v>1.903748513916942</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
